--- a/tif/data/Daftar mahasiswa 2025.xlsx
+++ b/tif/data/Daftar mahasiswa 2025.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10719"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nasikun/Programming/1. Personal web/a-nasikun.github.io/tif/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC32802-9C37-2346-A0F5-581731F642FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30240" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Daftar Mahasiswa" sheetId="1" r:id="rId4"/>
-    <sheet name="Worksheet" sheetId="2" r:id="rId5"/>
+    <sheet name="Daftar Mahasiswa" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2345" uniqueCount="959">
   <si>
     <t>Daftar Mahasiswa</t>
   </si>
@@ -2898,32 +2903,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -2934,20 +2928,23 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFf1f500"/>
+        <fgColor rgb="FFF1F500"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -2961,30 +2958,37 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -3274,54 +3278,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH109"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.570313" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:34" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
-      <c r="I1"/>
-      <c r="J1"/>
-      <c r="K1"/>
-      <c r="L1"/>
-      <c r="M1"/>
-      <c r="N1"/>
-      <c r="O1"/>
-      <c r="P1"/>
-      <c r="Q1"/>
-      <c r="R1"/>
-      <c r="S1"/>
-      <c r="T1"/>
-      <c r="U1"/>
-      <c r="V1"/>
-      <c r="W1"/>
-      <c r="X1"/>
-      <c r="Y1"/>
-      <c r="Z1"/>
-      <c r="AA1"/>
-      <c r="AB1"/>
-      <c r="AC1"/>
-      <c r="AD1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:34" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -3425,7 +3427,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3515,7 +3517,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -3605,7 +3607,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -3693,7 +3695,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -3783,7 +3785,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -3873,7 +3875,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -3963,7 +3965,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -4053,7 +4055,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -4143,7 +4145,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -4233,7 +4235,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -4323,7 +4325,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>11</v>
       </c>
@@ -4413,7 +4415,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>12</v>
       </c>
@@ -4503,7 +4505,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>13</v>
       </c>
@@ -4593,7 +4595,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>14</v>
       </c>
@@ -4683,7 +4685,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:34">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>15</v>
       </c>
@@ -4773,7 +4775,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>16</v>
       </c>
@@ -4863,7 +4865,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>17</v>
       </c>
@@ -4953,7 +4955,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>18</v>
       </c>
@@ -5043,7 +5045,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>19</v>
       </c>
@@ -5133,7 +5135,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>20</v>
       </c>
@@ -5223,7 +5225,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>21</v>
       </c>
@@ -5313,7 +5315,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>22</v>
       </c>
@@ -5403,7 +5405,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>23</v>
       </c>
@@ -5493,7 +5495,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>24</v>
       </c>
@@ -5583,7 +5585,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>25</v>
       </c>
@@ -5673,7 +5675,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>26</v>
       </c>
@@ -5763,7 +5765,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>27</v>
       </c>
@@ -5790,13 +5792,13 @@
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="M30" s="3">
         <v>37</v>
       </c>
       <c r="N30" s="3">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>191</v>
@@ -5853,7 +5855,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="1:34">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>28</v>
       </c>
@@ -5943,7 +5945,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="32" spans="1:34">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>29</v>
       </c>
@@ -6033,7 +6035,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:34">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -6123,7 +6125,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="34" spans="1:34">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>31</v>
       </c>
@@ -6213,7 +6215,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:34">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -6303,7 +6305,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:34">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -6393,7 +6395,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:34">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>34</v>
       </c>
@@ -6483,7 +6485,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:34">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -6571,7 +6573,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:34">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -6661,7 +6663,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:34">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>37</v>
       </c>
@@ -6751,7 +6753,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:34">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>38</v>
       </c>
@@ -6841,7 +6843,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:34">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>39</v>
       </c>
@@ -6931,7 +6933,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" spans="1:34">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>40</v>
       </c>
@@ -6958,13 +6960,13 @@
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="M43" s="3">
         <v>37</v>
       </c>
       <c r="N43" s="3">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>40</v>
@@ -7021,7 +7023,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="44" spans="1:34">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>41</v>
       </c>
@@ -7111,7 +7113,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:34">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>42</v>
       </c>
@@ -7201,7 +7203,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:34">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>43</v>
       </c>
@@ -7228,7 +7230,7 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="M46" s="3">
         <v>37</v>
@@ -7291,7 +7293,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="1:34">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>44</v>
       </c>
@@ -7381,7 +7383,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:34">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>45</v>
       </c>
@@ -7471,7 +7473,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:34">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>46</v>
       </c>
@@ -7561,7 +7563,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:34">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>47</v>
       </c>
@@ -7651,7 +7653,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:34">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>48</v>
       </c>
@@ -7741,7 +7743,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:34">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>49</v>
       </c>
@@ -7831,7 +7833,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:34">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>50</v>
       </c>
@@ -7921,7 +7923,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:34">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>51</v>
       </c>
@@ -8011,7 +8013,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="1:34">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>52</v>
       </c>
@@ -8101,7 +8103,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" spans="1:34">
+    <row r="56" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>53</v>
       </c>
@@ -8189,7 +8191,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="1:34">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>54</v>
       </c>
@@ -8279,7 +8281,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:34">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>55</v>
       </c>
@@ -8369,7 +8371,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="59" spans="1:34">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>56</v>
       </c>
@@ -8459,7 +8461,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:34">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>57</v>
       </c>
@@ -8549,7 +8551,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="61" spans="1:34">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>58</v>
       </c>
@@ -8639,7 +8641,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="62" spans="1:34">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>59</v>
       </c>
@@ -8729,7 +8731,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:34">
+    <row r="63" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>60</v>
       </c>
@@ -8819,7 +8821,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="64" spans="1:34">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>61</v>
       </c>
@@ -8909,7 +8911,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:34">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>62</v>
       </c>
@@ -8999,7 +9001,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:34">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>63</v>
       </c>
@@ -9089,7 +9091,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="1:34">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>64</v>
       </c>
@@ -9179,7 +9181,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" spans="1:34">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>65</v>
       </c>
@@ -9269,7 +9271,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:34">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>66</v>
       </c>
@@ -9359,7 +9361,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="70" spans="1:34">
+    <row r="70" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>67</v>
       </c>
@@ -9449,7 +9451,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" spans="1:34">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>68</v>
       </c>
@@ -9539,7 +9541,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="72" spans="1:34">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>69</v>
       </c>
@@ -9629,7 +9631,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="73" spans="1:34">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>70</v>
       </c>
@@ -9719,7 +9721,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="74" spans="1:34">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>71</v>
       </c>
@@ -9809,7 +9811,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:34">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>72</v>
       </c>
@@ -9842,7 +9844,7 @@
         <v>37</v>
       </c>
       <c r="N75" s="3">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>191</v>
@@ -9899,7 +9901,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="76" spans="1:34">
+    <row r="76" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>73</v>
       </c>
@@ -9989,7 +9991,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="77" spans="1:34">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>74</v>
       </c>
@@ -10079,7 +10081,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="78" spans="1:34">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>75</v>
       </c>
@@ -10169,7 +10171,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="79" spans="1:34">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>76</v>
       </c>
@@ -10259,7 +10261,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="80" spans="1:34">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>77</v>
       </c>
@@ -10349,7 +10351,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="81" spans="1:34">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>78</v>
       </c>
@@ -10439,7 +10441,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="1:34">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>79</v>
       </c>
@@ -10529,7 +10531,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="83" spans="1:34">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>80</v>
       </c>
@@ -10619,7 +10621,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="84" spans="1:34">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>81</v>
       </c>
@@ -10709,7 +10711,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="85" spans="1:34">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>82</v>
       </c>
@@ -10736,13 +10738,13 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="M85" s="3">
         <v>37</v>
       </c>
       <c r="N85" s="3">
-        <v>2.43</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>191</v>
@@ -10799,7 +10801,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="86" spans="1:34">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>83</v>
       </c>
@@ -10889,7 +10891,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="87" spans="1:34">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>84</v>
       </c>
@@ -10979,7 +10981,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="88" spans="1:34">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>85</v>
       </c>
@@ -11069,7 +11071,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="89" spans="1:34">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>86</v>
       </c>
@@ -11159,7 +11161,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:34">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>87</v>
       </c>
@@ -11249,7 +11251,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="91" spans="1:34">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>88</v>
       </c>
@@ -11339,7 +11341,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="92" spans="1:34">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>89</v>
       </c>
@@ -11429,7 +11431,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="93" spans="1:34">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>90</v>
       </c>
@@ -11519,7 +11521,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="94" spans="1:34">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>91</v>
       </c>
@@ -11609,7 +11611,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="95" spans="1:34">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>92</v>
       </c>
@@ -11699,7 +11701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="96" spans="1:34">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>93</v>
       </c>
@@ -11732,7 +11734,7 @@
         <v>37</v>
       </c>
       <c r="N96" s="3">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>191</v>
@@ -11787,7 +11789,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="97" spans="1:34">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>94</v>
       </c>
@@ -11814,7 +11816,7 @@
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M97" s="3">
         <v>39</v>
@@ -11877,7 +11879,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="98" spans="1:34">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>95</v>
       </c>
@@ -11967,7 +11969,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="99" spans="1:34">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>96</v>
       </c>
@@ -12000,7 +12002,7 @@
         <v>37</v>
       </c>
       <c r="N99" s="3">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="O99" s="3" t="s">
         <v>191</v>
@@ -12057,7 +12059,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="100" spans="1:34">
+    <row r="100" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>97</v>
       </c>
@@ -12147,7 +12149,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="1:34">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>98</v>
       </c>
@@ -12237,7 +12239,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="102" spans="1:34">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>99</v>
       </c>
@@ -12327,7 +12329,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="103" spans="1:34">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>100</v>
       </c>
@@ -12417,7 +12419,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:34">
+    <row r="104" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>101</v>
       </c>
@@ -12444,13 +12446,13 @@
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
       <c r="L104" s="3">
-        <v>2.05</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="M104" s="3">
         <v>37</v>
       </c>
       <c r="N104" s="3">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="O104" s="3" t="s">
         <v>191</v>
@@ -12507,7 +12509,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="105" spans="1:34">
+    <row r="105" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>102</v>
       </c>
@@ -12597,7 +12599,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="1:34">
+    <row r="106" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>103</v>
       </c>
@@ -12687,7 +12689,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="107" spans="1:34">
+    <row r="107" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>104</v>
       </c>
@@ -12777,7 +12779,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="108" spans="1:34">
+    <row r="108" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>105</v>
       </c>
@@ -12867,7 +12869,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="109" spans="1:34">
+    <row r="109" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>106</v>
       </c>
@@ -12958,43 +12960,22 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <mergeCells>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:AD1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>